--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.39834617003795</v>
+        <v>13.71473125263117</v>
       </c>
       <c r="D2" t="n">
-        <v>86.07449208806055</v>
+        <v>13.98710496430984</v>
       </c>
       <c r="E2" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F2" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>107.1703645914907</v>
+        <v>17.41518424611724</v>
       </c>
       <c r="D3" t="n">
-        <v>108.8999355132726</v>
+        <v>17.6962395209068</v>
       </c>
       <c r="E3" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F3" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.3212905338122</v>
+        <v>11.10220971174448</v>
       </c>
       <c r="D4" t="n">
-        <v>70.01226628870577</v>
+        <v>11.37699327191469</v>
       </c>
       <c r="E4" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F4" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.32912891802647</v>
+        <v>4.765983449179301</v>
       </c>
       <c r="D5" t="n">
-        <v>28.56658328600679</v>
+        <v>4.642069783976104</v>
       </c>
       <c r="E5" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F5" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.91098473571787</v>
+        <v>5.998035019554154</v>
       </c>
       <c r="D6" t="n">
-        <v>36.13747580395198</v>
+        <v>5.872339818142197</v>
       </c>
       <c r="E6" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F6" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.79425673564443</v>
+        <v>7.766566719542221</v>
       </c>
       <c r="D7" t="n">
-        <v>47.00987341148912</v>
+        <v>7.639104429366982</v>
       </c>
       <c r="E7" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F7" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.52839339465485</v>
+        <v>7.723363926631413</v>
       </c>
       <c r="D8" t="n">
-        <v>46.80169713849025</v>
+        <v>7.605275785004666</v>
       </c>
       <c r="E8" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F8" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.38380094698436</v>
+        <v>4.612367653884959</v>
       </c>
       <c r="D9" t="n">
-        <v>27.90868716389191</v>
+        <v>4.535161664132436</v>
       </c>
       <c r="E9" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F9" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>64.37709135393204</v>
+        <v>10.46127734501396</v>
       </c>
       <c r="D10" t="n">
-        <v>64.98097039531667</v>
+        <v>10.55940768923896</v>
       </c>
       <c r="E10" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F10" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>59.05668012272679</v>
+        <v>9.596710519943104</v>
       </c>
       <c r="D11" t="n">
-        <v>57.43669088257327</v>
+        <v>9.333462268418156</v>
       </c>
       <c r="E11" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F11" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>80.86880216771982</v>
+        <v>13.14118035225447</v>
       </c>
       <c r="D12" t="n">
-        <v>81.46116241274515</v>
+        <v>13.23743889207109</v>
       </c>
       <c r="E12" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F12" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.63892469239387</v>
+        <v>6.766325262514004</v>
       </c>
       <c r="D13" t="n">
-        <v>39.92776995824135</v>
+        <v>6.488262618214219</v>
       </c>
       <c r="E13" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F13" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.83366677173882</v>
+        <v>6.147970850407559</v>
       </c>
       <c r="D14" t="n">
-        <v>37.35347618070933</v>
+        <v>6.069939879365267</v>
       </c>
       <c r="E14" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F14" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>79.24650198126183</v>
+        <v>12.87755657195505</v>
       </c>
       <c r="D15" t="n">
-        <v>79.65935324668516</v>
+        <v>12.94464490258634</v>
       </c>
       <c r="E15" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F15" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.70223802911847</v>
+        <v>6.289113679731751</v>
       </c>
       <c r="D16" t="n">
-        <v>37.20111755655645</v>
+        <v>6.045181602940424</v>
       </c>
       <c r="E16" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F16" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.72695598362524</v>
+        <v>7.268130347339102</v>
       </c>
       <c r="D17" t="n">
-        <v>44.11185244592848</v>
+        <v>7.168176022463378</v>
       </c>
       <c r="E17" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F17" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>92.77006016057058</v>
+        <v>15.07513477609272</v>
       </c>
       <c r="D18" t="n">
-        <v>93.11264674429238</v>
+        <v>15.13080509594751</v>
       </c>
       <c r="E18" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F18" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>48.55797246868936</v>
+        <v>7.890670526162021</v>
       </c>
       <c r="D19" t="n">
-        <v>47.04740333553448</v>
+        <v>7.645203042024352</v>
       </c>
       <c r="E19" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F19" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.5296311198565</v>
+        <v>7.723565056976682</v>
       </c>
       <c r="D20" t="n">
-        <v>46.30151023838513</v>
+        <v>7.523995413737585</v>
       </c>
       <c r="E20" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F20" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>52.5475218997491</v>
+        <v>8.538972308709228</v>
       </c>
       <c r="D21" t="n">
-        <v>50.89402178661216</v>
+        <v>8.270278540324476</v>
       </c>
       <c r="E21" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F21" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>72.01303824273957</v>
+        <v>11.70211871444518</v>
       </c>
       <c r="D22" t="n">
-        <v>71.96561597901915</v>
+        <v>11.69441259659061</v>
       </c>
       <c r="E22" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F22" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>67.91180678536428</v>
+        <v>11.0356686026217</v>
       </c>
       <c r="D23" t="n">
-        <v>67.31459340830736</v>
+        <v>10.93862142884995</v>
       </c>
       <c r="E23" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F23" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>77.0245521846639</v>
+        <v>12.51648973000789</v>
       </c>
       <c r="D24" t="n">
-        <v>76.6435202326484</v>
+        <v>12.45457203780536</v>
       </c>
       <c r="E24" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F24" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>95.28762309016845</v>
+        <v>15.48423875215237</v>
       </c>
       <c r="D25" t="n">
-        <v>93.55478351890763</v>
+        <v>15.20265232182249</v>
       </c>
       <c r="E25" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F25" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>70.47913963529066</v>
+        <v>11.45286019073473</v>
       </c>
       <c r="D26" t="n">
-        <v>69.31772341609916</v>
+        <v>11.26413005511611</v>
       </c>
       <c r="E26" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F26" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>84.76656950881839</v>
+        <v>13.77456754518299</v>
       </c>
       <c r="D27" t="n">
-        <v>84.39226166742378</v>
+        <v>13.71374252095636</v>
       </c>
       <c r="E27" t="n">
-        <v>21.31386920161158</v>
+        <v>3.463503745261882</v>
       </c>
       <c r="F27" t="n">
-        <v>21.8733582934298</v>
+        <v>3.554420722682343</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
